--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_atacama_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_atacama_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:10</t>
+    <t xml:space="preserve">2026-09-29 14:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_atacama_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_atacama_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:06</t>
+    <t xml:space="preserve">2026-09-29 18:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -518,10 +518,10 @@
         <v>-22.81</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>54.32</v>
+        <v>54.33</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>77.13</v>
+        <v>77.14</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_atacama_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_atacama_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:38</t>
+    <t xml:space="preserve">2026-10-05 04:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
